--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="11144250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 03:35</t>
+          <t>2026-07-12 10:30</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,911 +1175,911 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>New York Yankees offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.709</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.221</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>8.109</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.709</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>5.2</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.221</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.109</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B77" s="32" t="n">
         <v>0.58</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H77" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.405</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs New York Yankees defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D80" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G80" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H80" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I80" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J80" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K80" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L80" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M80" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N80" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O80" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P80" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q80" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>5.291</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>3.814</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>7.609</v>
-      </c>
-      <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.291</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>4.5</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.435</v>
+        <v>3.814</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="32" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Q83" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="32" t="inlineStr"/>
+      <c r="J84" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="32" t="n">
+        <v>8.435</v>
+      </c>
+      <c r="Q84" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B85" s="32" t="n">
         <v>0.821</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C85" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D85" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E85" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F85" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G85" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H85" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I85" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="J85" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K85" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L85" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M85" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N85" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O85" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P85" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q85" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3026,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,250 +3043,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.272</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.852</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.272</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>6.1</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.918</v>
+        <v>4.852</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.739</v>
+        <v>8.304</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3350,22 +3271,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.239000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -3429,317 +3350,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.388</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.023</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>3.963</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.023</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.267</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.391</v>
+        <v>3.963</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3803,22 +3724,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.217</v>
+        <v>8.391</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -3882,68 +3803,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.587</v>
+        <v>1.217</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.675</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3962,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,246 +3979,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.853</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.366</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.853</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.6</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>4.366</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.312</v>
+        <v>7.854</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -4282,22 +4203,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.444</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.646000000000001</v>
+        <v>1.312</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -4361,317 +4282,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.778</v>
+        <v>1.444</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.427</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.233</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.463</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.659</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.042</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.659</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.167</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.979</v>
+        <v>4.042</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -4735,22 +4656,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.958</v>
+        <v>7.979</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -4814,68 +4735,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.333</v>
+        <v>0.958</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.512</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.378</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,899 +5843,899 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>3.919</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.271</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.919</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>3.8</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>4.271</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.494</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.647</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.647</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>4.133</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>9.388</v>
+        <v>4.07</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.361</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,13 +8836,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6431</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-180</v>
+        <v>-187</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6377999999999999</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-176</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5785</v>
+        <v>0.5899</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-137</v>
+        <v>-144</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9034,13 +9034,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5907</v>
+        <v>0.5918</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6252</v>
+        <v>0.5861</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-167</v>
+        <v>-142</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9162,17 +9162,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.6185</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-134</v>
+        <v>-162</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5531</v>
+        <v>0.5667</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-124</v>
+        <v>-131</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4215</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>137</v>
+        <v>-125</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -9355,22 +9355,22 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4093</v>
+        <v>0.5391</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>144</v>
+        <v>-117</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9430,13 +9430,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5182</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5174</v>
+        <v>0.5516</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-107</v>
+        <v>-123</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9538,37 +9538,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5584</v>
+        <v>0.4082</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-126</v>
+        <v>145</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-105</v>
+        <v>180</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9624,17 +9624,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6422</v>
+        <v>0.4101</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-179</v>
+        <v>144</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-144</v>
+        <v>178</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9675,32 +9675,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.469</v>
+        <v>0.5476</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>113</v>
+        <v>-121</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -9751,22 +9751,22 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5032</v>
+        <v>0.4709</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>112</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,32 +9807,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 182.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5147</v>
+        <v>0.5827</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-106</v>
+        <v>-140</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>-120</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9883,22 +9883,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5826</v>
+        <v>0.5154</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-140</v>
+        <v>-106</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-120</v>
+        <v>107</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,12 +9939,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 182.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5191</v>
+        <v>0.5122</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,14 +10020,14 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5306</v>
+        <v>0.5322</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>100</v>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,12 +10071,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4977</v>
+        <v>0.4818</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5808</v>
+        <v>0.6422</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-139</v>
+        <v>-179</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-122</v>
+        <v>-156</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,32 +10203,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.515</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-110</v>
+        <v>-106</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10269,32 +10269,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3954</v>
+        <v>0.514</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>153</v>
+        <v>-106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,32 +10335,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.5345</v>
       </c>
       <c r="G28" s="14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v>-104</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,32 +10401,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5166999999999999</v>
+        <v>0.5815</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-107</v>
+        <v>-139</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>101</v>
+        <v>-125</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4196</v>
+        <v>0.4527</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>113</v>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,13 +10693,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5804</v>
+        <v>0.5473</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-138</v>
+        <v>-121</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>105</v>
+        <v>-112</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10755,17 +10755,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6252</v>
+        <v>0.5516</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-167</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10821,17 +10821,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2836</v>
+        <v>0.4484</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>253</v>
+        <v>123</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 28.4% (fair +253). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4215</v>
+        <v>0.4101</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5785</v>
+        <v>0.5899</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-137</v>
+        <v>-144</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,10 +11023,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.42</v>
+        <v>0.4144</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>138</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.58</v>
+        <v>0.5856</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-138</v>
+        <v>-141</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-138</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11155,13 +11155,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4833</v>
+        <v>0.4451</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,13 +11221,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5166999999999999</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-107</v>
+        <v>-125</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,13 +11287,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4117</v>
+        <v>0.4143</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5883</v>
+        <v>0.5857</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-143</v>
+        <v>-141</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-144</v>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11419,13 +11419,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4751</v>
+        <v>0.4678</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,13 +11485,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.5322</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-110</v>
+        <v>-114</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11547,17 +11547,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4578</v>
+        <v>0.3727</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11613,17 +11613,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5476</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,13 +11683,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6277</v>
+        <v>0.6388</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-169</v>
+        <v>-177</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,13 +11749,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.3723</v>
+        <v>0.3612</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5826</v>
+        <v>0.5827</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-140</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4174</v>
+        <v>0.4173</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>140</v>
@@ -11947,13 +11947,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5191</v>
+        <v>0.5154</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4809</v>
+        <v>0.4846</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-104</v>
+        <v>-107</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.531</v>
+        <v>0.5291</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-133</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12145,13 +12145,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.469</v>
+        <v>0.4709</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4968</v>
+        <v>0.486</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-107</v>
+        <v>-102</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,13 +12277,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5032</v>
+        <v>0.514</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-101</v>
+        <v>-106</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12339,17 +12339,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.363</v>
+        <v>0.4609</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12405,17 +12405,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5531</v>
+        <v>0.5391</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-124</v>
+        <v>-117</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12481,7 +12481,7 @@
         <v>-179</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4406</v>
+        <v>0.4349</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5594</v>
+        <v>0.5651</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-127</v>
+        <v>-130</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12735,17 +12735,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4614</v>
+        <v>0.5206</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>117</v>
+        <v>-109</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12801,17 +12801,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4463</v>
+        <v>0.4794</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3683</v>
+        <v>0.3736</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 37.4% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6316999999999999</v>
+        <v>0.6264000000000001</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-172</v>
+        <v>-168</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-170</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 62.6% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4776</v>
+        <v>0.4585</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13069,13 +13069,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5224</v>
+        <v>0.5415</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-109</v>
+        <v>-118</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-103</v>
+        <v>-117</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-134</v>
+        <v>-142</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,13 +13201,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4278999999999999</v>
+        <v>0.4139</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,13 +13267,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3569</v>
+        <v>0.3483</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +180). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,13 +13333,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6431</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-180</v>
+        <v>-187</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13399,13 +13399,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4694</v>
+        <v>0.4655</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13465,13 +13465,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5306</v>
+        <v>0.5345</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13531,13 +13531,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4977</v>
+        <v>0.5667</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>101</v>
+        <v>-131</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,13 +13597,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5023</v>
+        <v>0.4333</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-101</v>
+        <v>131</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4093</v>
+        <v>0.4082</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>180</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,13 +13729,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5907</v>
+        <v>0.5918</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13795,13 +13795,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4192</v>
+        <v>0.4185</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>139</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5808</v>
+        <v>0.5815</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-139</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13923,17 +13923,17 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4368</v>
+        <v>0.4818</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13989,17 +13989,17 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4763999999999999</v>
+        <v>0.5182</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>110</v>
+        <v>-108</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,13 +14059,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3954</v>
+        <v>0.3957</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>153</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6046</v>
+        <v>0.6043000000000001</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-153</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14191,13 +14191,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4722</v>
+        <v>0.4540392</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14257,13 +14257,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5278</v>
+        <v>0.5459608</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-112</v>
+        <v>-120</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-107</v>
+        <v>-102</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5174</v>
+        <v>0.6185</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-107</v>
+        <v>-162</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14385,17 +14385,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3961</v>
+        <v>0.3815</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +152). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,7 +14455,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.3622</v>
+        <v>0.3624</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>176</v>
@@ -14521,13 +14521,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.6377999999999999</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>-176</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3901</v>
+        <v>0.3939</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6099</v>
+        <v>0.6061</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-156</v>
+        <v>-154</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4655</v>
+        <v>0.459</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.541</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4519</v>
+        <v>0.4527</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>121</v>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5481</v>
+        <v>0.5473</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>-121</v>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5194</v>
+        <v>0.5221</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4806</v>
+        <v>0.4779</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15374,7 +15374,7 @@
         <v>-209</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15440,7 +15440,7 @@
         <v>209</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15496,17 +15496,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 176.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6109380322653482</v>
+        <v>0.5651807350850266</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-157</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -15562,17 +15562,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 176.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3890619677346518</v>
+        <v>0.4348192649149734</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -15638,7 +15638,7 @@
         <v>-148</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15704,7 +15704,7 @@
         <v>148</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15836,7 +15836,7 @@
         <v>-150</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -15892,17 +15892,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 176.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.2726872194756316</v>
+        <v>0.2350387557655145</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 27.3% (fair +267). Your call.</t>
+          <t>Model 23.5% (fair +325). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15958,17 +15958,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 176.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.7273127805243684</v>
+        <v>0.7649612442344855</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-267</v>
+        <v>-325</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 72.7% (fair -267). Your call.</t>
+          <t>Model 76.5% (fair -325). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16024,17 +16024,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -4.5</t>
+          <t>Washington Mystics -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5056541107365459</v>
+        <v>0.4430238296467474</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-102</v>
+        <v>126</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16090,17 +16090,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +4.5</t>
+          <t>Seattle Storm +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4943458892634541</v>
+        <v>0.5569761703532526</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>102</v>
+        <v>-126</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16166,7 +16166,7 @@
         <v>356</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16232,7 +16232,7 @@
         <v>-356</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.515</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4905</v>
+        <v>0.485</v>
       </c>
       <c r="G20" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="H20" s="15" t="n">
         <v>104</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>-105</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16424,13 +16424,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16490,10 +16490,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4923999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>100</v>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16562,7 +16562,7 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -16688,10 +16688,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5147</v>
+        <v>0.5122</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>108</v>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -16754,13 +16754,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4853</v>
+        <v>0.4878</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -16816,17 +16816,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -6.5</t>
+          <t>Las Vegas Aces -5.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4365025644033865</v>
+        <v>0.467680273555499</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -16882,14 +16882,14 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +6.5</t>
+          <t>Indiana Fever +5.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5634974355966135</v>
+        <v>0.532319726444501</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-129</v>
+        <v>-114</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>138</v>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -16958,7 +16958,7 @@
         <v>202</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -17024,7 +17024,7 @@
         <v>-202</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -17080,17 +17080,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5584</v>
+        <v>0.5324</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-126</v>
+        <v>-114</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17146,17 +17146,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 179.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4416</v>
+        <v>0.4676</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17212,17 +17212,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -7.5</t>
+          <t>Atlanta Dream -9.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.3905243127429648</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-110</v>
+        <v>122</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17278,17 +17278,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +7.5</t>
+          <t>Los Angeles Sparks +9.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.6094756872570352</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-109</v>
+        <v>-156</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -17354,7 +17354,7 @@
         <v>1157</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -17420,7 +17420,7 @@
         <v>-1157</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -17476,17 +17476,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5016</v>
+        <v>0.5144</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-101</v>
+        <v>-106</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -17542,17 +17542,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 170.5</t>
+          <t>Under 169.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4984</v>
+        <v>0.4856</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -17608,17 +17608,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -11.5</t>
+          <t>Minnesota Lynx -12.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.4956</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-107</v>
+        <v>102</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -17674,17 +17674,17 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +11.5</t>
+          <t>Phoenix Mercury +12.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.5044</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>107</v>
+        <v>-102</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 10:30</t>
+          <t>2026-07-12 12:07</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,167 +2115,246 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.585</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>5.145</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.033</v>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.585</v>
+        <v>8.106</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -2339,22 +2418,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.106</v>
+        <v>1.383</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.104</v>
+        <v>8.458</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -2418,313 +2497,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.383</v>
+        <v>7.404</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.439</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.404</v>
+        <v>0.519</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>3.976</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>3.976</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
+        <v>7.404</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.333</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.723</v>
+        <v>7.896</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.404</v>
+        <v>1.213</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -2788,22 +2867,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.896</v>
+        <v>1.354</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.213</v>
+        <v>9.532</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -2867,147 +2946,68 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.354</v>
+        <v>7.708</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>9.532</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.519</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.2</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.708</v>
+        <v>0.415</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3026,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,171 +3043,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs New York Mets defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.272</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.852</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.272</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.1</v>
+        <v>8.304</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.852</v>
+        <v>7.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.304</v>
+        <v>0.739</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3271,22 +3350,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.918</v>
+        <v>0.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.739</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -3350,317 +3429,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.918</v>
+        <v>9.061</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.239000000000001</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.388</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.8</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.061</v>
+        <v>0.536</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E75" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Boston Red Sox defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="L78" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.023</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
+        <v>7.306</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>3.267</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>3.963</v>
+        <v>8.391</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.306</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3724,22 +3803,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.391</v>
+        <v>1.217</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -3803,147 +3882,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.217</v>
+        <v>8.587</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.536</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.367</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.587</v>
+        <v>0.675</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3962,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,167 +3979,246 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.366</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>3.853</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>7.854</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>3.6</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.366</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.854</v>
+        <v>1.312</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -4203,22 +4282,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.312</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -4282,317 +4361,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.646000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.427</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.778</v>
+        <v>0.463</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.659</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.042</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.659</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.167</v>
+        <v>8.778</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.042</v>
+        <v>7.979</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -4656,22 +4735,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.979</v>
+        <v>0.958</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -4735,147 +4814,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.958</v>
+        <v>8.333</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.244</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.512</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.3</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.333</v>
+        <v>0.378</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4894,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4911,167 +4911,246 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Detroit Tigers defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Detroit Tigers defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.442</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.442</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>7.234</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>3.267</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>3.854</v>
+        <v>7.592</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.234</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -5135,22 +5214,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.592</v>
+        <v>0.898</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.213</v>
+        <v>8.426</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5214,317 +5293,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.898</v>
+        <v>7.776</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.53</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.167</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.776</v>
+        <v>0.329</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Detroit Tigers offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Detroit Tigers offense vs Philadelphia Phillies defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.872</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>5.033</v>
+        <v>7.755</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.872</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.755</v>
+        <v>1.02</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -5588,22 +5667,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>9.319000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.02</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5667,147 +5746,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.17</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,167 +5843,325 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.919</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.919</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>0.959</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.8</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.271</v>
+        <v>1.082</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.735</v>
+        <v>8</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6067,392 +6225,392 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.694</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.494</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.082</v>
+        <v>0.578</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.531000000000001</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.647</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+      <c r="K77" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.647</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>0.918</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.133</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.07</v>
+        <v>1.143</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.286</v>
+        <v>7.816</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6516,226 +6674,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.939</v>
+        <v>9.388</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.578</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.433</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.143</v>
+        <v>0.361</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>9.388</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6477999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-187</v>
+        <v>-184</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.2% (fair -187). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6158</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-176</v>
+        <v>-160</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.5992999999999999</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-144</v>
+        <v>-150</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9034,13 +9034,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5918</v>
+        <v>0.583</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-145</v>
+        <v>-140</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5861</v>
+        <v>0.5851</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-142</v>
+        <v>-141</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>127</v>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6185</v>
+        <v>0.6109</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-162</v>
+        <v>-157</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>113</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5667</v>
+        <v>0.6362</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-131</v>
+        <v>-175</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>122</v>
+        <v>-102</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9298,13 +9298,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5589</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5391</v>
+        <v>0.5669</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-117</v>
+        <v>-131</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.5385</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9496,13 +9496,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5206</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-123</v>
+        <v>-109</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.417</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>180</v>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9609,32 +9609,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.5709</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>144</v>
+        <v>-133</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5476</v>
+        <v>0.5523</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9756,17 +9756,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Toronto Tempo +6.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4709</v>
+        <v>0.5484</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>112</v>
+        <v>-121</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,32 +9807,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5827</v>
+        <v>0.4007</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-140</v>
+        <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-120</v>
+        <v>178</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5154</v>
+        <v>0.5289</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-106</v>
+        <v>-112</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 182.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5314</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,32 +10005,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5322</v>
+        <v>0.4673</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-114</v>
+        <v>114</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,12 +10071,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4818</v>
+        <v>0.5293</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>108</v>
+        <v>-112</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6422</v>
+        <v>0.5828</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-179</v>
+        <v>-140</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-156</v>
+        <v>-124</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,32 +10203,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.515</v>
+        <v>0.5093</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10264,37 +10264,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.514</v>
+        <v>0.5245</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,32 +10335,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.3983</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-115</v>
+        <v>151</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-104</v>
+        <v>163</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,32 +10401,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5815</v>
+        <v>0.5125</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-139</v>
+        <v>-105</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-125</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.452</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>121</v>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,13 +10693,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.548</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10759,13 +10759,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5523</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10825,13 +10825,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4484</v>
+        <v>0.4477</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.4007</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.5992999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-144</v>
+        <v>-150</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4144</v>
+        <v>0.4142</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>141</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5856</v>
+        <v>0.5858</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-141</v>
@@ -11155,13 +11155,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4451</v>
+        <v>0.4411</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,13 +11221,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5589</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,13 +11287,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4143</v>
+        <v>0.4159</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5857</v>
+        <v>0.5841000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-144</v>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11419,13 +11419,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4678</v>
+        <v>0.4594</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,13 +11485,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5322</v>
+        <v>0.5406</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-114</v>
+        <v>-118</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11551,13 +11551,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3727</v>
+        <v>0.3902</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5476</v>
+        <v>0.5293</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-121</v>
+        <v>-112</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,13 +11683,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6388</v>
+        <v>0.6424</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-177</v>
+        <v>-180</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 64.2% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,13 +11749,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.3612</v>
+        <v>0.3576</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 35.8% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5827</v>
+        <v>0.5633</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-140</v>
+        <v>-129</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-120</v>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,13 +11881,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4173</v>
+        <v>0.4367</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11947,13 +11947,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5154</v>
+        <v>0.5669</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-106</v>
+        <v>-131</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4846</v>
+        <v>0.4331</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-107</v>
+        <v>101</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5291</v>
+        <v>0.5327</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-133</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4709</v>
+        <v>0.4673</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>127</v>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.486</v>
+        <v>0.4907</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,13 +12277,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.514</v>
+        <v>0.5093</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4609</v>
+        <v>0.4615</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>117</v>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12409,13 +12409,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5391</v>
+        <v>0.5385</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-117</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6422</v>
+        <v>0.6191</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-179</v>
+        <v>-163</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-156</v>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3578</v>
+        <v>0.3809</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4349</v>
+        <v>0.4328</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5651</v>
+        <v>0.5672</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-133</v>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12735,17 +12735,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.461</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-109</v>
+        <v>117</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12801,17 +12801,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.4467999999999999</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3736</v>
+        <v>0.379</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +168). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6264000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-168</v>
+        <v>-164</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -168). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4585</v>
+        <v>0.4518</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13069,13 +13069,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.5482</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5861</v>
+        <v>0.5851</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-142</v>
+        <v>-141</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>127</v>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,13 +13201,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4139</v>
+        <v>0.4149</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,13 +13267,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3483</v>
+        <v>0.3522</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 34.8% (fair +187). Your call.</t>
+          <t>Model 35.2% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6477999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-187</v>
+        <v>-184</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>186</v>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 65.2% (fair -187). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13399,10 +13399,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4655</v>
+        <v>0.4686</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>104</v>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13465,13 +13465,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.5314</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13531,13 +13531,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5667</v>
+        <v>0.5206</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-131</v>
+        <v>-109</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,13 +13597,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4333</v>
+        <v>0.4794</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.417</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>180</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,13 +13729,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5918</v>
+        <v>0.583</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-145</v>
+        <v>-140</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13795,13 +13795,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4185</v>
+        <v>0.4172</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5815</v>
+        <v>0.5828</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13927,13 +13927,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4818</v>
+        <v>0.4291</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,13 +13993,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.5709</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-108</v>
+        <v>-133</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,13 +14059,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3957</v>
+        <v>0.3983</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6043000000000001</v>
+        <v>0.6017</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-153</v>
+        <v>-151</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-170</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14191,13 +14191,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4540392</v>
+        <v>0.4388216</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14257,13 +14257,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5459608</v>
+        <v>0.5611784</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.6185</v>
+        <v>0.6109</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-162</v>
+        <v>-157</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>113</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3815</v>
+        <v>0.3891</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,13 +14455,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.3624</v>
+        <v>0.3842</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 36.2% (fair +176). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6158</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-176</v>
+        <v>-160</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>178</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3939</v>
+        <v>0.4551</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6061</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-154</v>
+        <v>-120</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.417</v>
+        <v>0.4042</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.583</v>
+        <v>0.5958</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-140</v>
+        <v>-147</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.4548</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.5452</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5216</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>-109</v>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4784</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>109</v>
@@ -15440,7 +15440,7 @@
         <v>209</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15500,10 +15500,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5651807350850266</v>
+        <v>0.5289</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-130</v>
+        <v>-112</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>104</v>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -15566,13 +15566,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4348192649149734</v>
+        <v>0.4711</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -15632,13 +15632,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5967260576454791</v>
+        <v>0.5484</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-148</v>
+        <v>-121</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4032739423545209</v>
+        <v>0.4516</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>104</v>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.2350387557655145</v>
+        <v>0.3638</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>104</v>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 23.5% (fair +325). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15962,13 +15962,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.7649612442344855</v>
+        <v>0.6362</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-325</v>
+        <v>-175</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 76.5% (fair -325). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16100,7 +16100,7 @@
         <v>-126</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16232,7 +16232,7 @@
         <v>-356</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.515</v>
+        <v>0.5125</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.485</v>
+        <v>0.4875</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16420,17 +16420,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings -9.5</t>
+          <t>Dallas Wings -10.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.51</v>
+        <v>0.4931</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-104</v>
+        <v>103</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16486,14 +16486,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +9.5</t>
+          <t>Chicago Sky +10.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.49</v>
+        <v>0.5069</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>104</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>100</v>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16688,13 +16688,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5171</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -16754,10 +16754,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4878</v>
+        <v>0.4829</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-104</v>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -16826,7 +16826,7 @@
         <v>114</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -17084,13 +17084,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5324</v>
+        <v>0.5245</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17150,13 +17150,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4676</v>
+        <v>0.4755</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17222,7 +17222,7 @@
         <v>156</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -17288,7 +17288,7 @@
         <v>-156</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-108</v>
+        <v>-107</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17480,13 +17480,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5144</v>
+        <v>0.512</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4856</v>
+        <v>0.488</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-105</v>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -17608,17 +17608,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -12.5</t>
+          <t>Minnesota Lynx -13.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4956</v>
+        <v>0.486</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>104</v>
+        <v>-106</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -17674,14 +17674,14 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury +12.5</t>
+          <t>Phoenix Mercury +13.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5044</v>
+        <v>0.514</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-102</v>
+        <v>-106</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>100</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 12:07</t>
+          <t>2026-07-12 14:06</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,246 +2115,167 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>5.145</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.585</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.438000000000001</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.145</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.033</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>8.106</v>
+        <v>4.585</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.104</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -2418,22 +2339,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.383</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.458</v>
+        <v>1.104</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -2497,313 +2418,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.404</v>
+        <v>1.383</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.439</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="36" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>3.976</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.404</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.976</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.333</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>7.896</v>
+        <v>4.723</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.213</v>
+        <v>7.404</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -2867,22 +2788,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.354</v>
+        <v>7.896</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>9.532</v>
+        <v>1.213</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -2946,68 +2867,147 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.708</v>
+        <v>1.354</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>9.532</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H81" s="34" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="36" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.415</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7686,7 +7686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7703,167 +7703,246 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Athletics offense vs Chicago White Sox defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Athletics offense vs Chicago White Sox defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.602</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
+        <v>8.146000000000001</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.167</v>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.602</v>
+        <v>7.854</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>1.062</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -7927,22 +8006,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.854</v>
+        <v>1.062</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.062</v>
+        <v>8.625</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -8006,313 +8085,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.062</v>
+        <v>7.938</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.625</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.578</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.5669999999999999</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.938</v>
+        <v>0.531</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Chicago White Sox offense vs Athletics defense</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Chicago White Sox offense vs Athletics defense</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.819</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>6.767</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.819</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>7.792</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>6.767</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P77" s="32" t="n">
-        <v>5.333</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.792</v>
+        <v>1.354</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -8376,22 +8455,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>1.271</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.354</v>
+        <v>9.208</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -8455,147 +8534,68 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.271</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>9.208</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.7</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6477999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-184</v>
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6158</v>
+        <v>0.7493000000000001</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-160</v>
+        <v>-299</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 74.9% (fair -299). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5992999999999999</v>
+        <v>0.6158</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-150</v>
+        <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.583</v>
+        <v>0.6412</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-140</v>
+        <v>-179</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,32 +9081,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5851</v>
+        <v>0.5899</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-141</v>
+        <v>-144</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9147,32 +9147,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6109</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-157</v>
+        <v>-140</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,32 +9213,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6362</v>
+        <v>0.583</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-175</v>
+        <v>-140</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-102</v>
+        <v>163</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9298,13 +9298,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5589</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-127</v>
+        <v>-175</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5813</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-131</v>
+        <v>-139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.5589</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5669</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-109</v>
+        <v>-131</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9543,32 +9543,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.417</v>
+        <v>0.6374</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>140</v>
+        <v>-176</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>180</v>
+        <v>-104</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9609,32 +9609,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.417</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-133</v>
+        <v>140</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5523</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-123</v>
+        <v>-117</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,32 +9741,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo +6.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5484</v>
+        <v>0.5516</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,32 +9807,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4007</v>
+        <v>0.5123</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>150</v>
+        <v>-105</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5709</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-112</v>
+        <v>-133</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5314</v>
+        <v>0.5378000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-113</v>
+        <v>-116</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.4101</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10081,22 +10081,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5293</v>
+        <v>0.416</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-112</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5828</v>
+        <v>0.5233</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-140</v>
+        <v>-110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-124</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10213,22 +10213,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5093</v>
+        <v>0.5206</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-104</v>
+        <v>-109</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10264,17 +10264,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10284,17 +10284,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5245</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,32 +10335,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.3983</v>
+        <v>0.5249</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>151</v>
+        <v>-110</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,32 +10401,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5125</v>
+        <v>0.5816</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-105</v>
+        <v>-139</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>-122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.452</v>
+        <v>0.4438</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,13 +10693,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.548</v>
+        <v>0.5562</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-121</v>
+        <v>-125</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10759,13 +10759,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5523</v>
+        <v>0.5516</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10825,13 +10825,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4477</v>
+        <v>0.4484</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>112</v>
+        <v>-102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4007</v>
+        <v>0.4101</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5992999999999999</v>
+        <v>0.5899</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11227,7 +11227,7 @@
         <v>-127</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11419,13 +11419,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.4505</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,13 +11485,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5495</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-118</v>
+        <v>-122</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11547,17 +11547,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3902</v>
+        <v>0.4622</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11613,17 +11613,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5293</v>
+        <v>0.5378000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-112</v>
+        <v>-116</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6424</v>
+        <v>0.416</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-180</v>
+        <v>140</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-170</v>
+        <v>165</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -180). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11745,17 +11745,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.3576</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>180</v>
+        <v>-140</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +180). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,13 +11815,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5633</v>
+        <v>0.5645</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4367</v>
+        <v>0.4355</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>119</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11953,7 +11953,7 @@
         <v>-131</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -12019,7 +12019,7 @@
         <v>131</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12075,17 +12075,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Cincinnati Reds -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.2507</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-114</v>
+        <v>299</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-133</v>
+        <v>-108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 25.1% (fair +299). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12141,17 +12141,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.7493000000000001</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>114</v>
+        <v>-299</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 74.9% (fair -299). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4907</v>
+        <v>0.4893999999999999</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>104</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,13 +12277,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5093</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-104</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12339,17 +12339,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4615</v>
+        <v>0.3634</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12405,17 +12405,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-117</v>
+        <v>-175</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12471,17 +12471,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>New York Mets -1.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6191</v>
+        <v>0.3588</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-163</v>
+        <v>179</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-156</v>
+        <v>122</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -163). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12537,14 +12537,14 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3809</v>
+        <v>0.6412</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>163</v>
+        <v>-179</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>156</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +163). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4328</v>
+        <v>0.4202</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5672</v>
+        <v>0.5798</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-131</v>
+        <v>-138</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
@@ -12745,7 +12745,7 @@
         <v>117</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12801,14 +12801,14 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4467999999999999</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>124</v>
+        <v>-117</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>117</v>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,13 +12871,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.379</v>
+        <v>0.3828</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.621</v>
+        <v>0.6172</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-164</v>
+        <v>-161</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4518</v>
+        <v>0.4509</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5482</v>
+        <v>0.5491</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>-122</v>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5851</v>
+        <v>0.5813</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-141</v>
+        <v>-139</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>127</v>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,13 +13201,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4149</v>
+        <v>0.4187</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3522</v>
+        <v>0.3525</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>184</v>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6477999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-184</v>
@@ -13399,13 +13399,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4686</v>
+        <v>0.4751</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13465,13 +13465,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5314</v>
+        <v>0.5249</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
@@ -13537,7 +13537,7 @@
         <v>-109</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13593,17 +13593,17 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.3874000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13669,7 +13669,7 @@
         <v>140</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13735,7 +13735,7 @@
         <v>-140</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13795,10 +13795,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4172</v>
+        <v>0.4184</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>122</v>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5828</v>
+        <v>0.5816</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13933,7 +13933,7 @@
         <v>133</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13999,7 +13999,7 @@
         <v>-133</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3983</v>
+        <v>0.3993</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>163</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,13 +14125,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6017</v>
+        <v>0.6007</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-151</v>
+        <v>-150</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-170</v>
+        <v>-167</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14197,7 +14197,7 @@
         <v>128</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.6109</v>
+        <v>0.5123</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-157</v>
+        <v>-105</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14385,17 +14385,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3891</v>
+        <v>0.4877</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.541</v>
+        <v>0.54</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4548</v>
+        <v>0.4395</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 44.0% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5452</v>
+        <v>0.5605</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 56.0% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5216</v>
+        <v>0.5426</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-109</v>
+        <v>-119</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4574</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15374,7 +15374,7 @@
         <v>-209</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15440,7 +15440,7 @@
         <v>209</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-112</v>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -15566,13 +15566,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4711</v>
+        <v>0.4723000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -15632,13 +15632,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5484</v>
+        <v>0.5967260576454791</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-121</v>
+        <v>-148</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -15698,13 +15698,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4516</v>
+        <v>0.4032739423545209</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3638</v>
+        <v>0.3626</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>104</v>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15962,13 +15962,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6362</v>
+        <v>0.6374</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16100,7 +16100,7 @@
         <v>-126</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16166,7 +16166,7 @@
         <v>356</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5125</v>
+        <v>0.5138</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4875</v>
+        <v>0.4862</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16684,17 +16684,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 182.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5171</v>
+        <v>0.5233</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-107</v>
+        <v>-110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -16750,17 +16750,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 182.5</t>
+          <t>Under 181.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4829</v>
+        <v>0.4767</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -16816,17 +16816,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -5.5</t>
+          <t>Las Vegas Aces -4.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.467680273555499</v>
+        <v>0.4990576175368866</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -16882,14 +16882,14 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +5.5</t>
+          <t>Indiana Fever +4.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.532319726444501</v>
+        <v>0.5009423824631134</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-114</v>
+        <v>-100</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>138</v>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -16958,7 +16958,7 @@
         <v>202</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -17024,7 +17024,7 @@
         <v>-202</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -17084,13 +17084,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5245</v>
+        <v>0.5275</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17150,13 +17150,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4755</v>
+        <v>0.4725</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17354,7 +17354,7 @@
         <v>1157</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>614</v>
+        <v>570</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -19217,7 +19217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19234,167 +19234,246 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Baltimore Orioles defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.279</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.279</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>7.792</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.133</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.75</v>
+        <v>8.833</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -19458,22 +19537,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.833</v>
+        <v>1.062</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -19537,317 +19616,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.062</v>
+        <v>8</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.53</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.633</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8</v>
+        <v>0.458</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Kansas City Royals defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.571</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>5.291</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>6.167</v>
+        <v>8.208</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>5.291</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.208</v>
+        <v>1.271</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -19911,22 +19990,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.271</v>
+        <v>8.917</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -19990,147 +20069,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.917</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.494</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.208</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 14:06</t>
+          <t>2026-07-12 15:17</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,246 +3979,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.853</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.366</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.853</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.6</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>4.366</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.312</v>
+        <v>7.854</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -4282,22 +4203,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.444</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.646000000000001</v>
+        <v>1.312</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -4361,317 +4282,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.778</v>
+        <v>1.444</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.427</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.233</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.463</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.659</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.042</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.659</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.167</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.979</v>
+        <v>4.042</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -4735,22 +4656,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.958</v>
+        <v>7.979</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -4814,68 +4735,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.333</v>
+        <v>0.958</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.512</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.378</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4894,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4911,246 +4911,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.442</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>3.854</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.442</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.267</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.592</v>
+        <v>3.854</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.213</v>
+        <v>7.234</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -5214,22 +5135,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>0.898</v>
+        <v>7.592</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.426</v>
+        <v>1.213</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5293,317 +5214,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.776</v>
+        <v>0.898</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.53</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>13th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.167</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.872</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.755</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.39</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.033</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>9.319000000000001</v>
+        <v>4.872</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.02</v>
+        <v>7.755</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -5667,22 +5588,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.17</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5746,68 +5667,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7686,7 +7686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7703,246 +7703,167 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Athletics offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.602</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.146000000000001</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.506</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.167</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>7.854</v>
+        <v>4.602</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.062</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -8006,22 +7927,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.062</v>
+        <v>7.854</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.625</v>
+        <v>1.062</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -8085,313 +8006,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.938</v>
+        <v>1.062</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="36" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.531</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Athletics defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.819</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>6.767</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.819</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>6.767</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>5.333</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.354</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -8455,22 +8376,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.271</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>9.208</v>
+        <v>1.354</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -8534,68 +8455,147 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>1.271</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H81" s="34" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.711</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7493000000000001</v>
+        <v>0.6158</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-299</v>
+        <v>-160</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 74.9% (fair -299). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6158</v>
+        <v>0.5899</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-160</v>
+        <v>-144</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6412</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-179</v>
+        <v>-140</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.583</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-144</v>
+        <v>-140</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9147,32 +9147,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5840000000000001</v>
+        <v>0.6109</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-140</v>
+        <v>-157</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -9223,22 +9223,22 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.583</v>
+        <v>0.5813</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9298,13 +9298,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5548</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-175</v>
+        <v>-125</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5813</v>
+        <v>0.635</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-139</v>
+        <v>-174</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5589</v>
+        <v>0.5669</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-127</v>
+        <v>-131</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9492,14 +9492,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5372</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-131</v>
+        <v>-116</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>122</v>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9543,32 +9543,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6374</v>
+        <v>0.417</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-176</v>
+        <v>140</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-104</v>
+        <v>185</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -176). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -9619,22 +9619,22 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.417</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>140</v>
+        <v>-117</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9756,17 +9756,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5709</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-123</v>
+        <v>-133</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,12 +9807,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9822,17 +9822,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5123</v>
+        <v>0.5378000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-105</v>
+        <v>-116</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,32 +9873,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.4101</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-133</v>
+        <v>144</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9949,22 +9949,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5378000000000001</v>
+        <v>0.416</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-116</v>
+        <v>140</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,32 +10005,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.5233</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>144</v>
+        <v>-110</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10066,17 +10066,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Los Angeles Sparks +9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.416</v>
+        <v>0.5614</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>140</v>
+        <v>-128</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>165</v>
+        <v>-107</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,12 +10137,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10152,17 +10152,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5233</v>
+        <v>0.5301</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10269,29 +10269,29 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5249</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>104</v>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10345,22 +10345,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.4627</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-110</v>
+        <v>116</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11023,10 +11023,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4142</v>
+        <v>0.4191</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>138</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5858</v>
+        <v>0.5809</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-141</v>
+        <v>-139</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-138</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4411</v>
+        <v>0.4452</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>100</v>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5589</v>
+        <v>0.5548</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>129</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4159</v>
+        <v>0.416</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>140</v>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5841000000000001</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-140</v>
@@ -12075,17 +12075,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds -1.5</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.2507</v>
+        <v>0.5373</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>299</v>
+        <v>-116</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 25.1% (fair +299). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12141,14 +12141,14 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.7493000000000001</v>
+        <v>0.4627</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-299</v>
+        <v>116</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>130</v>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 74.9% (fair -299). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12339,17 +12339,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3634</v>
+        <v>0.4628</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12405,17 +12405,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5372</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-175</v>
+        <v>-116</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12471,17 +12471,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>New York Mets -1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3588</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>179</v>
+        <v>-163</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>122</v>
+        <v>-156</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12537,14 +12537,14 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6412</v>
+        <v>0.3804999999999999</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-179</v>
+        <v>163</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>156</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3993</v>
+        <v>0.4007</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>150</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,13 +14125,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6007</v>
+        <v>0.5992999999999999</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-150</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-167</v>
+        <v>-163</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5123</v>
+        <v>0.6109</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-105</v>
+        <v>-157</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14385,17 +14385,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4877</v>
+        <v>0.3891</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.46</v>
+        <v>0.4581</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.54</v>
+        <v>0.5419</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.4408</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +128). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5592</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -128). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5426</v>
+        <v>0.5446</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4574</v>
+        <v>0.4554</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15374,7 +15374,7 @@
         <v>-209</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15500,10 +15500,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5301</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>104</v>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -15566,13 +15566,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4723000000000001</v>
+        <v>0.4699</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -15704,7 +15704,7 @@
         <v>148</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3626</v>
+        <v>0.365</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>104</v>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +176). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15962,13 +15962,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6374</v>
+        <v>0.635</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-176</v>
+        <v>-174</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -176). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16034,7 +16034,7 @@
         <v>126</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Over 178</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5138</v>
+        <v>0.5416954029096943</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-106</v>
+        <v>-118</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16354,17 +16354,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Under 178</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4862</v>
+        <v>0.4350045970903057</v>
       </c>
       <c r="G20" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="H20" s="15" t="n">
         <v>106</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16420,17 +16420,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings -10.5</t>
+          <t>Dallas Wings -9.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.5149</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>103</v>
+        <v>-106</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16486,17 +16486,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +10.5</t>
+          <t>Chicago Sky +9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5069</v>
+        <v>0.4851</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>106</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16562,7 +16562,7 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -16826,7 +16826,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -17024,7 +17024,7 @@
         <v>-202</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -17080,17 +17080,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 180.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5275</v>
+        <v>0.5181</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17146,14 +17146,14 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 180.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4725</v>
+        <v>0.4819</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>-104</v>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17216,13 +17216,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3905243127429648</v>
+        <v>0.4386</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17282,10 +17282,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6094756872570352</v>
+        <v>0.5614</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-156</v>
+        <v>-128</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-107</v>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -17480,13 +17480,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.512</v>
+        <v>0.5144</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.488</v>
+        <v>0.4856</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-105</v>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -17612,13 +17612,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.486</v>
+        <v>0.4794</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -17678,13 +17678,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.514</v>
+        <v>0.5206</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-106</v>
+        <v>-109</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -19217,7 +19217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19234,246 +19234,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.279</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.279</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>4.133</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.833</v>
+        <v>4.75</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.896</v>
+        <v>7.792</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -19537,22 +19458,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.062</v>
+        <v>8.833</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.021000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -19616,317 +19537,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8</v>
+        <v>1.062</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.53</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.458</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>6.167</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>5.291</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.571</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>6.167</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>5.291</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.271</v>
+        <v>8.208</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -19990,22 +19911,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.25</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.917</v>
+        <v>1.271</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -20069,68 +19990,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.208</v>
+        <v>1.25</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.494</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.8070000000000001</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10201275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 15:17</t>
+          <t>2026-07-12 16:58</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,167 +2115,325 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>4.585</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>5.145</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>1.104</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.033</v>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.585</v>
+        <v>1.383</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -2339,392 +2497,392 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.106</v>
+        <v>7.404</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.439</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.383</v>
+        <v>0.519</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>3.976</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
         <v>7.404</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>3.976</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
+        <v>1.213</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.333</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.723</v>
+        <v>1.354</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.404</v>
+        <v>9.532</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -2788,226 +2946,68 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.519</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>0.2</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.354</v>
+        <v>0.415</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>9.532</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3026,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,250 +3043,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.272</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.852</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.272</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>6.1</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.918</v>
+        <v>4.852</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.739</v>
+        <v>8.304</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3350,22 +3271,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.239000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -3429,317 +3350,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.388</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.023</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>3.963</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.023</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.267</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.391</v>
+        <v>3.963</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3803,22 +3724,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.217</v>
+        <v>8.391</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -3882,68 +3803,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.587</v>
+        <v>1.217</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.675</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,325 +5843,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.919</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.271</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.919</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>3.8</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.082</v>
+        <v>4.271</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6225,392 +6067,392 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>7.694</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.494</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.647</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.647</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>4.133</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.143</v>
+        <v>4.07</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.816</v>
+        <v>8.286</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6674,68 +6516,226 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.361</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6475</v>
+        <v>0.6553</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-184</v>
+        <v>-190</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6158</v>
+        <v>0.5965</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-160</v>
+        <v>-148</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-144</v>
+        <v>-142</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5840000000000001</v>
+        <v>0.5908</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-140</v>
+        <v>-144</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.583</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-140</v>
+        <v>-149</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>163</v>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6109</v>
+        <v>0.625</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-157</v>
+        <v>-167</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>122</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5813</v>
+        <v>0.5787</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-139</v>
+        <v>-137</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>127</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Seattle Storm @ Washington Mystics</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9294,17 +9294,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5548</v>
+        <v>0.635</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-125</v>
+        <v>-174</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.635</v>
+        <v>0.572</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-174</v>
+        <v>-134</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-131</v>
+        <v>-124</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5372</v>
+        <v>0.5367999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>-116</v>
@@ -9543,32 +9543,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.417</v>
+        <v>0.5601</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>140</v>
+        <v>-127</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.5387</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-117</v>
@@ -9685,22 +9685,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.4138</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-123</v>
+        <v>142</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.5403</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>-118</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,32 +9807,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5378000000000001</v>
+        <v>0.4017</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-116</v>
+        <v>149</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,32 +9873,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.5216</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144</v>
+        <v>-109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.416</v>
+        <v>0.4092</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>165</v>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>New York Liberty @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5233</v>
+        <v>0.5301</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10066,37 +10066,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5614</v>
+        <v>0.5392</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-128</v>
+        <v>-117</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-107</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.4667</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-113</v>
+        <v>114</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5182</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>107</v>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10345,22 +10345,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4627</v>
+        <v>0.5817</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>116</v>
+        <v>-139</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>130</v>
+        <v>-122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5601</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-123</v>
+        <v>-127</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>111</v>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4484</v>
+        <v>0.4399</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-102</v>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.4138</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-144</v>
+        <v>-142</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,10 +11023,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4191</v>
+        <v>0.4002</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>138</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5809</v>
+        <v>0.5998</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-139</v>
+        <v>-150</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-138</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4452</v>
+        <v>0.4471</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>100</v>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5548</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>129</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,10 +11287,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.416</v>
+        <v>0.4184</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>142</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5840000000000001</v>
+        <v>0.5816</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-144</v>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11551,10 +11551,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4622</v>
+        <v>0.4597</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5378000000000001</v>
+        <v>0.5403</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>112</v>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.416</v>
+        <v>0.4092</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>165</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5840000000000001</v>
+        <v>0.5908</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-140</v>
+        <v>-144</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>170</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5645</v>
+        <v>0.5817</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-130</v>
+        <v>-139</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-122</v>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4355</v>
+        <v>0.4183</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>119</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.572</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-131</v>
+        <v>-134</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>122</v>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.428</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>126</v>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5373</v>
+        <v>0.5333</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-116</v>
+        <v>-114</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-138</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4627</v>
+        <v>0.4667</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>130</v>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,10 +12211,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4893999999999999</v>
+        <v>0.4889</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>-104</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,10 +12277,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5111</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>104</v>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4628</v>
+        <v>0.4632</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>116</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5372</v>
+        <v>0.5367999999999999</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-116</v>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6197</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>-163</v>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3804999999999999</v>
+        <v>0.3803</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>163</v>
@@ -12607,10 +12607,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4202</v>
+        <v>0.4229000000000001</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>144</v>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5798</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-144</v>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12739,7 +12739,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.461</v>
+        <v>0.4613</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>117</v>
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.5387</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-117</v>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3828</v>
+        <v>0.381</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>156</v>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6172</v>
+        <v>0.619</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-156</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4509</v>
+        <v>0.4513</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>122</v>
@@ -13069,7 +13069,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5491</v>
+        <v>0.5487</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>-122</v>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5813</v>
+        <v>0.5787</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-139</v>
+        <v>-137</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>127</v>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,10 +13201,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4187</v>
+        <v>0.4213</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>105</v>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,10 +13267,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3525</v>
+        <v>0.3447</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>186</v>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 35.2% (fair +184). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6475</v>
+        <v>0.6553</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-184</v>
+        <v>-190</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>186</v>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 64.8% (fair -184). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5182</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>107</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3874000000000001</v>
+        <v>0.3897</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>104</v>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.417</v>
+        <v>0.4017</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>185</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,10 +13729,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.583</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-140</v>
+        <v>-149</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>163</v>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4291</v>
+        <v>0.4608</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>113</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.5392</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>100</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4007</v>
+        <v>0.4008</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>150</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5992999999999999</v>
+        <v>0.5992</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-150</v>
@@ -14191,10 +14191,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4388216</v>
+        <v>0.4200912</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>138</v>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14257,10 +14257,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5611784</v>
+        <v>0.5799088</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-128</v>
+        <v>-138</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>-104</v>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.6109</v>
+        <v>0.625</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-157</v>
+        <v>-167</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>122</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3891</v>
+        <v>0.375</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>122</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 37.5% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.3842</v>
+        <v>0.4035</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>156</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.6158</v>
+        <v>0.5965</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-160</v>
+        <v>-148</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>178</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4551</v>
+        <v>0.4561</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-120</v>
+        <v>-119</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4581</v>
+        <v>0.4549</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5419</v>
+        <v>0.5451</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4408</v>
+        <v>0.4429</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5592</v>
+        <v>0.5571</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5446</v>
+        <v>0.5445</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>-120</v>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.4% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4554</v>
+        <v>0.4555</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>120</v>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.6% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -16166,7 +16166,7 @@
         <v>356</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 178</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5416954029096943</v>
+        <v>0.5113</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16354,17 +16354,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 178</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4350045970903057</v>
+        <v>0.4887</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>106</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5149</v>
+        <v>0.5137</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>-106</v>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16490,13 +16490,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4851</v>
+        <v>0.4863</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>106</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16562,7 +16562,7 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -16688,10 +16688,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5233</v>
+        <v>0.5216</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>108</v>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -16754,13 +16754,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4767</v>
+        <v>0.4784</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -16816,17 +16816,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -4.5</t>
+          <t>Las Vegas Aces -6.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4990576175368866</v>
+        <v>0.4365025644033865</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -16882,14 +16882,14 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +4.5</t>
+          <t>Indiana Fever +6.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5009423824631134</v>
+        <v>0.5634974355966135</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-100</v>
+        <v>-129</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>138</v>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -16958,7 +16958,7 @@
         <v>202</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -17084,10 +17084,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.5254</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>-108</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17150,13 +17150,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.4746</v>
       </c>
       <c r="G32" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="H32" s="15" t="n">
         <v>108</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17212,17 +17212,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -9.5</t>
+          <t>Atlanta Dream -8.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4386</v>
+        <v>0.4210482224080958</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17278,17 +17278,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +9.5</t>
+          <t>Los Angeles Sparks +8.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5614</v>
+        <v>0.5789517775919042</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-128</v>
+        <v>-138</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-107</v>
+        <v>127</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -17354,7 +17354,7 @@
         <v>1157</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>570</v>
+        <v>669</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -17480,13 +17480,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5144</v>
+        <v>0.5095</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4856</v>
+        <v>0.4905</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-105</v>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -17612,13 +17612,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.486</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -17678,13 +17678,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.514</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -17823,28 +17823,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2494</v>
+        <v>0.2489</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>558</v>
+        <v>587</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3881</v>
+        <v>0.3979</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-85.47</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-15.43</v>
+        <v>-12.92</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>4.36</v>
+        <v>3.98</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="6">
@@ -17854,28 +17854,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2503</v>
+        <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>497</v>
+        <v>526</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3834</v>
+        <v>0.3946</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-83.48999999999999</v>
+        <v>-73.33</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-16.93</v>
+        <v>-14.05</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>6.21</v>
+        <v>5.73</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5532</v>
+        <v>0.5533</v>
       </c>
     </row>
     <row r="7">
@@ -17958,7 +17958,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=402, ECE 0.044 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=412, ECE 0.045 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -18034,16 +18034,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>0.3663</v>
+        <v>0.3662</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.5263</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.1742</v>
+        <v>0.1602</v>
       </c>
     </row>
     <row r="20">
@@ -18053,16 +18053,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4588</v>
+        <v>0.459</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.4297</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0257</v>
+        <v>-0.0294</v>
       </c>
     </row>
     <row r="21">
@@ -18072,16 +18072,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5426</v>
+        <v>0.5429</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5407</v>
+        <v>0.5389</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0019</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10201275"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 16:58</t>
+          <t>2026-07-12 18:01</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,325 +2115,167 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>5.145</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>4.585</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.438000000000001</v>
-      </c>
-      <c r="C68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.106</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.145</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.033</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>1.383</v>
+        <v>4.585</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.458</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -2497,392 +2339,392 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.404</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.439</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>3.976</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>7.404</v>
-      </c>
-      <c r="C76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.896</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.976</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.333</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>1.354</v>
+        <v>4.723</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>9.532</v>
+        <v>7.404</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -2946,68 +2788,226 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.708</v>
+        <v>7.896</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>9.532</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="34" t="inlineStr">
+      <c r="H81" s="34" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="36" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.415</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6754,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6771,171 +6771,250 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels offense vs Minnesota Twins defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.595</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.167</v>
+        <v>7.714</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.976</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.714</v>
+        <v>1.184</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -6999,22 +7078,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.184</v>
+        <v>9.286</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7078,313 +7157,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.918</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.286</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.59</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.367</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs Los Angeles Angels defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs Los Angeles Angels defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.807</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.807</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>7.776</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.633</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>5.131</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -7448,22 +7527,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.244999999999999</v>
+        <v>1.061</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7527,147 +7606,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.061</v>
+        <v>8.816000000000001</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.939</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.5669999999999999</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.816000000000001</v>
+        <v>0.578</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6553</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-190</v>
+        <v>-195</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5965</v>
+        <v>0.5876</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-148</v>
+        <v>-142</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8964,17 +8964,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.601</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-142</v>
+        <v>-151</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5908</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-144</v>
+        <v>-130</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5739000000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-149</v>
+        <v>-135</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.625</v>
+        <v>0.6242</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-167</v>
+        <v>-166</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>122</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5787</v>
+        <v>0.5655</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-137</v>
+        <v>-130</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>127</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9294,17 +9294,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.635</v>
+        <v>0.5772</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-174</v>
+        <v>-137</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.572</v>
+        <v>0.5575</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-134</v>
+        <v>-126</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5501</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-116</v>
+        <v>-134</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9553,22 +9553,22 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5601</v>
+        <v>0.434</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-127</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5387</v>
+        <v>0.5321</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-117</v>
+        <v>-114</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>117</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4138</v>
+        <v>0.399</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9760,10 +9760,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.5336000000000001</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-118</v>
+        <v>-114</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>112</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9807,12 +9807,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9822,17 +9822,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4017</v>
+        <v>0.4261</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9892,13 +9892,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5216</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4092</v>
+        <v>0.5249</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>144</v>
+        <v>-110</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.5347</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,32 +10071,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5392</v>
+        <v>0.4628</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-117</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.5816</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>114</v>
+        <v>-139</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>130</v>
+        <v>-122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,32 +10203,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.4124</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-108</v>
+        <v>142</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10269,32 +10269,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.4012</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-110</v>
+        <v>149</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10345,22 +10345,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.5095</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-139</v>
+        <v>-104</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-122</v>
+        <v>107</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,32 +10401,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5125</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-139</v>
+        <v>-105</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4438</v>
+        <v>0.4351</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>118</v>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5562</v>
+        <v>0.5649</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-125</v>
+        <v>-130</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-120</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5601</v>
+        <v>0.5725</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-127</v>
+        <v>-134</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>111</v>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4399</v>
+        <v>0.4275</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-102</v>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4138</v>
+        <v>0.434</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-142</v>
+        <v>-130</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,10 +11023,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4002</v>
+        <v>0.3987000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>138</v>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5998</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-138</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4471</v>
+        <v>0.4425</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>100</v>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5575</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>129</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,10 +11287,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4184</v>
+        <v>0.422</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>142</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5780000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-139</v>
+        <v>-137</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-144</v>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4505</v>
+        <v>0.4471000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>115</v>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,10 +11485,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5495</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-113</v>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11551,10 +11551,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4597</v>
+        <v>0.4664</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.5336000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-118</v>
+        <v>-114</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>112</v>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4092</v>
+        <v>0.4261</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>165</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5908</v>
+        <v>0.5739000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-144</v>
+        <v>-135</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>170</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.5723</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-139</v>
+        <v>-134</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-122</v>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4183</v>
+        <v>0.4277</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>119</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.572</v>
+        <v>0.5772</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-134</v>
+        <v>-137</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>122</v>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.428</v>
+        <v>0.4228</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>126</v>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5333</v>
+        <v>0.5372</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-114</v>
+        <v>-116</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-138</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12145,10 +12145,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.4628</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>130</v>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4889</v>
+        <v>0.488</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>105</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5111</v>
+        <v>0.512</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-105</v>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4632</v>
+        <v>0.4499</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>122</v>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.5501</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-116</v>
+        <v>-122</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>122</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6197</v>
+        <v>0.6212</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-156</v>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3803</v>
+        <v>0.3788</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>156</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12607,10 +12607,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4229000000000001</v>
+        <v>0.4247</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>144</v>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5753</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-144</v>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4613</v>
+        <v>0.4679</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>118</v>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5387</v>
+        <v>0.5321</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-117</v>
+        <v>-114</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>117</v>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.381</v>
+        <v>0.3789</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>156</v>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.619</v>
+        <v>0.6211</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>-156</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5787</v>
+        <v>0.5655</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-137</v>
+        <v>-130</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>127</v>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,10 +13201,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4213</v>
+        <v>0.4345</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>105</v>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,10 +13267,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3447</v>
+        <v>0.3392</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>186</v>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6553</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-190</v>
+        <v>-195</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>186</v>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.5095</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>107</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3897</v>
+        <v>0.3983</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>104</v>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4017</v>
+        <v>0.399</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>185</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,10 +13729,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.601</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>163</v>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4608</v>
+        <v>0.4653</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>113</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5392</v>
+        <v>0.5347</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>100</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4008</v>
+        <v>0.4012</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>163</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5992</v>
+        <v>0.5988</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-150</v>
+        <v>-149</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-163</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4200912</v>
+        <v>0.4196</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>138</v>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5799088</v>
+        <v>0.5804</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>-138</v>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.625</v>
+        <v>0.6242</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-167</v>
+        <v>-166</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>122</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.375</v>
+        <v>0.3758</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>122</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4035</v>
+        <v>0.4124</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>156</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5965</v>
+        <v>0.5876</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-148</v>
+        <v>-142</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>178</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4561</v>
+        <v>0.4608</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5392</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4042</v>
+        <v>0.4079</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +147). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5958</v>
+        <v>0.5921</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4549</v>
+        <v>0.4581</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5451</v>
+        <v>0.5419</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4429</v>
+        <v>0.4422</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>126</v>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5571</v>
+        <v>0.5578</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>-126</v>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5445</v>
+        <v>0.5392</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4555</v>
+        <v>0.4608</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +120). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15224,7 +15224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -15364,17 +15364,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Chicago Sky</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.67647</v>
+        <v>0.2190888999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-209</v>
+        <v>356</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-115</v>
+        <v>400</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 67.6% (fair -209). Your call.</t>
+          <t>Model 21.9% (fair +356). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -15415,12 +15415,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -15430,17 +15430,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.32353</v>
+        <v>0.7809111000000001</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>209</v>
+        <v>-356</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>257</v>
+        <v>-115</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 32.4% (fair +209). Your call.</t>
+          <t>Model 78.1% (fair -356). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -15481,12 +15481,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -15500,10 +15500,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.5125</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-113</v>
+        <v>-105</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>104</v>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -15547,12 +15547,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4699</v>
+        <v>0.4875</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -15613,12 +15613,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -15628,17 +15628,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo +6.5</t>
+          <t>Dallas Wings -9.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5967260576454791</v>
+        <v>0.5162</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-148</v>
+        <v>-107</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -15679,12 +15679,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Toronto Tempo</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -15694,17 +15694,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty -6.5</t>
+          <t>Chicago Sky +9.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4032739423545209</v>
+        <v>0.4838</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -15745,12 +15745,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
@@ -15836,7 +15836,7 @@
         <v>-150</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -15877,12 +15877,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -15892,17 +15892,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.365</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>174</v>
+        <v>-108</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15943,12 +15943,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -15958,17 +15958,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Under 181.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.635</v>
+        <v>0.4814000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-174</v>
+        <v>108</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16009,12 +16009,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -16024,17 +16024,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -6.5</t>
+          <t>Las Vegas Aces -6</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4430238296467474</v>
+        <v>0.4520544547810846</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16075,12 +16075,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Washington Mystics</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -16090,17 +16090,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +6.5</t>
+          <t>Indiana Fever +6</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5569761703532526</v>
+        <v>0.5167455452189154</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-126</v>
+        <v>-107</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16136,12 +16136,12 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -16156,17 +16156,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Los Angeles Sparks</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.2190888999999999</v>
+        <v>0.331247</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>356</v>
+        <v>202</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>413</v>
+        <v>285</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 21.9% (fair +356). Your call.</t>
+          <t>Model 33.1% (fair +202). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16202,12 +16202,12 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -16222,17 +16222,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>Atlanta Dream</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.7809111000000001</v>
+        <v>0.668753</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-356</v>
+        <v>-202</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 78.1% (fair -356). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16268,12 +16268,12 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -16288,17 +16288,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Over 180.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5113</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G19" s="14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>-105</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16334,12 +16334,12 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -16354,17 +16354,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 178.5</t>
+          <t>Under 180.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4887</v>
+        <v>0.4762999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-102</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16400,12 +16400,12 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -16420,17 +16420,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings -9.5</t>
+          <t>Atlanta Dream -8.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5137</v>
+        <v>0.4210482224080958</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-106</v>
+        <v>138</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16466,12 +16466,12 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -16486,17 +16486,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +9.5</t>
+          <t>Los Angeles Sparks +8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4863</v>
+        <v>0.5789517775919042</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>106</v>
+        <v>-138</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16532,12 +16532,12 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -16552,17 +16552,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4</v>
+        <v>0.07955000000000001</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>150</v>
+        <v>1157</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>182</v>
+        <v>733</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 8.0% (fair +1157). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -16598,12 +16598,12 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -16618,17 +16618,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6</v>
+        <v>0.92045</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-150</v>
+        <v>-1157</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 92.0% (fair -1157). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -16664,12 +16664,12 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -16684,17 +16684,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5216</v>
+        <v>0.5095</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-109</v>
+        <v>-104</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -16730,12 +16730,12 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -16750,17 +16750,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 181.5</t>
+          <t>Under 169.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4905</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -16796,12 +16796,12 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -16816,17 +16816,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -6.5</t>
+          <t>Minnesota Lynx -13.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4365025644033865</v>
+        <v>0.486</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>-106</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -16862,12 +16862,12 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>Phoenix Mercury @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -16882,17 +16882,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +6.5</t>
+          <t>Phoenix Mercury +13.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5634974355966135</v>
+        <v>0.514</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-129</v>
+        <v>-106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -16925,801 +16925,9 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>0.331247</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="I29" s="13">
-        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
-        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L29" s="18">
-        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M29" s="12">
-        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="inlineStr">
-        <is>
-          <t>Model 33.1% (fair +202). Your call.</t>
-        </is>
-      </c>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="16">
-        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>0.668753</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>-202</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>-120</v>
-      </c>
-      <c r="I30" s="13">
-        <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
-        <v/>
-      </c>
-      <c r="J30" s="16">
-        <f>IF($H$30="","",$F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
-        <f>IF($H$30="","",MAX(0,($F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))/IF($H$30&lt;0,-100/$H$30,$H$30/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L30" s="18">
-        <f>IF($H$30="","",ROUND(MIN($K$30,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M30" s="12">
-        <f>IF($J$30="","",IF($J$30&lt;0,"Pass",IF($J$30&lt;'Settings'!$B$4,"Thin",IF($J$30&lt;0.06,"✅ Sharp band",IF($J$30&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N30" s="19" t="inlineStr">
-        <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
-        </is>
-      </c>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="16">
-        <f>IF(OR($H$30="",$O$30=""),"",(1+IF($H$30&lt;0,-100/$H$30,$H$30/100))/(1+IF($O$30&lt;0,-100/$O$30,$O$30/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Over 180.5</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>0.5254</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I31" s="13">
-        <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
-        <v/>
-      </c>
-      <c r="J31" s="16">
-        <f>IF($H$31="","",$F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
-        <f>IF($H$31="","",MAX(0,($F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))/IF($H$31&lt;0,-100/$H$31,$H$31/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L31" s="18">
-        <f>IF($H$31="","",ROUND(MIN($K$31,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M31" s="12">
-        <f>IF($J$31="","",IF($J$31&lt;0,"Pass",IF($J$31&lt;'Settings'!$B$4,"Thin",IF($J$31&lt;0.06,"✅ Sharp band",IF($J$31&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
-        <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
-        </is>
-      </c>
-      <c r="O31" s="15" t="n"/>
-      <c r="P31" s="16">
-        <f>IF(OR($H$31="",$O$31=""),"",(1+IF($H$31&lt;0,-100/$H$31,$H$31/100))/(1+IF($O$31&lt;0,-100/$O$31,$O$31/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>Under 180.5</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>0.4746</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="I32" s="13">
-        <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
-        <v/>
-      </c>
-      <c r="J32" s="16">
-        <f>IF($H$32="","",$F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>IF($H$32="","",MAX(0,($F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))/IF($H$32&lt;0,-100/$H$32,$H$32/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L32" s="18">
-        <f>IF($H$32="","",ROUND(MIN($K$32,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M32" s="12">
-        <f>IF($J$32="","",IF($J$32&lt;0,"Pass",IF($J$32&lt;'Settings'!$B$4,"Thin",IF($J$32&lt;0.06,"✅ Sharp band",IF($J$32&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N32" s="19" t="inlineStr">
-        <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
-        </is>
-      </c>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="16">
-        <f>IF(OR($H$32="",$O$32=""),"",(1+IF($H$32&lt;0,-100/$H$32,$H$32/100))/(1+IF($O$32&lt;0,-100/$O$32,$O$32/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Atlanta Dream -8.5</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>0.4210482224080958</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>138</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="13">
-        <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
-        <v/>
-      </c>
-      <c r="J33" s="16">
-        <f>IF($H$33="","",$F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
-        <f>IF($H$33="","",MAX(0,($F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))/IF($H$33&lt;0,-100/$H$33,$H$33/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L33" s="18">
-        <f>IF($H$33="","",ROUND(MIN($K$33,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M33" s="12">
-        <f>IF($J$33="","",IF($J$33&lt;0,"Pass",IF($J$33&lt;'Settings'!$B$4,"Thin",IF($J$33&lt;0.06,"✅ Sharp band",IF($J$33&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N33" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
-        </is>
-      </c>
-      <c r="O33" s="15" t="n"/>
-      <c r="P33" s="16">
-        <f>IF(OR($H$33="",$O$33=""),"",(1+IF($H$33&lt;0,-100/$H$33,$H$33/100))/(1+IF($O$33&lt;0,-100/$O$33,$O$33/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks @ Atlanta Dream</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks +8.5</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>0.5789517775919042</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>127</v>
-      </c>
-      <c r="I34" s="13">
-        <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
-        <v/>
-      </c>
-      <c r="J34" s="16">
-        <f>IF($H$34="","",$F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="17">
-        <f>IF($H$34="","",MAX(0,($F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))/IF($H$34&lt;0,-100/$H$34,$H$34/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L34" s="18">
-        <f>IF($H$34="","",ROUND(MIN($K$34,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M34" s="12">
-        <f>IF($J$34="","",IF($J$34&lt;0,"Pass",IF($J$34&lt;'Settings'!$B$4,"Thin",IF($J$34&lt;0.06,"✅ Sharp band",IF($J$34&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N34" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
-        </is>
-      </c>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="16">
-        <f>IF(OR($H$34="",$O$34=""),"",(1+IF($H$34&lt;0,-100/$H$34,$H$34/100))/(1+IF($O$34&lt;0,-100/$O$34,$O$34/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>0.07955000000000001</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>1157</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>669</v>
-      </c>
-      <c r="I35" s="13">
-        <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
-        <v/>
-      </c>
-      <c r="J35" s="16">
-        <f>IF($H$35="","",$F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
-        <f>IF($H$35="","",MAX(0,($F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))/IF($H$35&lt;0,-100/$H$35,$H$35/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L35" s="18">
-        <f>IF($H$35="","",ROUND(MIN($K$35,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M35" s="12">
-        <f>IF($J$35="","",IF($J$35&lt;0,"Pass",IF($J$35&lt;'Settings'!$B$4,"Thin",IF($J$35&lt;0.06,"✅ Sharp band",IF($J$35&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N35" s="19" t="inlineStr">
-        <is>
-          <t>Model 8.0% (fair +1157). Your call.</t>
-        </is>
-      </c>
-      <c r="O35" s="15" t="n"/>
-      <c r="P35" s="16">
-        <f>IF(OR($H$35="",$O$35=""),"",(1+IF($H$35&lt;0,-100/$H$35,$H$35/100))/(1+IF($O$35&lt;0,-100/$O$35,$O$35/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>0.92045</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>-1157</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I36" s="13">
-        <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
-        <v/>
-      </c>
-      <c r="J36" s="16">
-        <f>IF($H$36="","",$F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
-        <f>IF($H$36="","",MAX(0,($F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))/IF($H$36&lt;0,-100/$H$36,$H$36/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L36" s="18">
-        <f>IF($H$36="","",ROUND(MIN($K$36,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M36" s="12">
-        <f>IF($J$36="","",IF($J$36&lt;0,"Pass",IF($J$36&lt;'Settings'!$B$4,"Thin",IF($J$36&lt;0.06,"✅ Sharp band",IF($J$36&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>Model 92.0% (fair -1157). Your call.</t>
-        </is>
-      </c>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="16">
-        <f>IF(OR($H$36="",$O$36=""),"",(1+IF($H$36&lt;0,-100/$H$36,$H$36/100))/(1+IF($O$36&lt;0,-100/$O$36,$O$36/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Over 169.5</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>0.5095</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>-104</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="I37" s="13">
-        <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
-        <v/>
-      </c>
-      <c r="J37" s="16">
-        <f>IF($H$37="","",$F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
-        <f>IF($H$37="","",MAX(0,($F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))/IF($H$37&lt;0,-100/$H$37,$H$37/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L37" s="18">
-        <f>IF($H$37="","",ROUND(MIN($K$37,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M37" s="12">
-        <f>IF($J$37="","",IF($J$37&lt;0,"Pass",IF($J$37&lt;'Settings'!$B$4,"Thin",IF($J$37&lt;0.06,"✅ Sharp band",IF($J$37&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N37" s="19" t="inlineStr">
-        <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
-        </is>
-      </c>
-      <c r="O37" s="15" t="n"/>
-      <c r="P37" s="16">
-        <f>IF(OR($H$37="",$O$37=""),"",(1+IF($H$37&lt;0,-100/$H$37,$H$37/100))/(1+IF($O$37&lt;0,-100/$O$37,$O$37/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>Under 169.5</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>0.4905</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>104</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I38" s="13">
-        <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
-        <v/>
-      </c>
-      <c r="J38" s="16">
-        <f>IF($H$38="","",$F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="17">
-        <f>IF($H$38="","",MAX(0,($F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))/IF($H$38&lt;0,-100/$H$38,$H$38/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L38" s="18">
-        <f>IF($H$38="","",ROUND(MIN($K$38,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M38" s="12">
-        <f>IF($J$38="","",IF($J$38&lt;0,"Pass",IF($J$38&lt;'Settings'!$B$4,"Thin",IF($J$38&lt;0.06,"✅ Sharp band",IF($J$38&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N38" s="19" t="inlineStr">
-        <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
-        </is>
-      </c>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="16">
-        <f>IF(OR($H$38="",$O$38=""),"",(1+IF($H$38&lt;0,-100/$H$38,$H$38/100))/(1+IF($O$38&lt;0,-100/$O$38,$O$38/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx -13.5</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>106</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I39" s="13">
-        <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
-        <v/>
-      </c>
-      <c r="J39" s="16">
-        <f>IF($H$39="","",$F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="17">
-        <f>IF($H$39="","",MAX(0,($F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))/IF($H$39&lt;0,-100/$H$39,$H$39/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L39" s="18">
-        <f>IF($H$39="","",ROUND(MIN($K$39,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M39" s="12">
-        <f>IF($J$39="","",IF($J$39&lt;0,"Pass",IF($J$39&lt;'Settings'!$B$4,"Thin",IF($J$39&lt;0.06,"✅ Sharp band",IF($J$39&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N39" s="19" t="inlineStr">
-        <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
-        </is>
-      </c>
-      <c r="O39" s="15" t="n"/>
-      <c r="P39" s="16">
-        <f>IF(OR($H$39="",$O$39=""),"",(1+IF($H$39&lt;0,-100/$H$39,$H$39/100))/(1+IF($O$39&lt;0,-100/$O$39,$O$39/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury +13.5</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="G40" s="14" t="n">
-        <v>-106</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="13">
-        <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
-        <v/>
-      </c>
-      <c r="J40" s="16">
-        <f>IF($H$40="","",$F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="17">
-        <f>IF($H$40="","",MAX(0,($F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))/IF($H$40&lt;0,-100/$H$40,$H$40/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L40" s="18">
-        <f>IF($H$40="","",ROUND(MIN($K$40,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M40" s="12">
-        <f>IF($J$40="","",IF($J$40&lt;0,"Pass",IF($J$40&lt;'Settings'!$B$4,"Thin",IF($J$40&lt;0.06,"✅ Sharp band",IF($J$40&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
-        <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
-        </is>
-      </c>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="16">
-        <f>IF(OR($H$40="",$O$40=""),"",(1+IF($H$40&lt;0,-100/$H$40,$H$40/100))/(1+IF($O$40&lt;0,-100/$O$40,$O$40/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J40">
+  <conditionalFormatting sqref="J5:J28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -17823,28 +17031,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2489</v>
+        <v>0.2488</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3979</v>
+        <v>0.3956</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-75.31999999999999</v>
+        <v>-79.88</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-12.92</v>
+        <v>-13.45</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>3.98</v>
+        <v>4.11</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5336</v>
+        <v>0.5353</v>
       </c>
     </row>
     <row r="6">
@@ -17854,28 +17062,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2498</v>
+        <v>0.2497</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3946</v>
+        <v>0.3921</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-73.33</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-14.05</v>
+        <v>-14.62</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>5.73</v>
+        <v>5.86</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5533</v>
+        <v>0.5551</v>
       </c>
     </row>
     <row r="7">
@@ -17958,7 +17166,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=412, ECE 0.045 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=414, ECE 0.045 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -18072,16 +17280,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5429</v>
+        <v>0.5431</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5389</v>
+        <v>0.5385</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.004</v>
+        <v>-0.0047</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 18:01</t>
+          <t>2026-07-12 19:04</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,167 +5843,325 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.919</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.919</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>0.959</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.8</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.271</v>
+        <v>1.082</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.735</v>
+        <v>8</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6067,392 +6225,392 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.694</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.494</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.082</v>
+        <v>0.578</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.531000000000001</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.647</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+      <c r="K77" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.647</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>0.918</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.133</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.07</v>
+        <v>1.143</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.286</v>
+        <v>7.816</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6516,226 +6674,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.939</v>
+        <v>9.388</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.578</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.433</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.143</v>
+        <v>0.361</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>9.388</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6754,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6771,250 +6771,171 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Angels offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.595</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.976</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.595</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.167</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>4.976</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.184</v>
+        <v>7.714</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -7078,22 +6999,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>0.918</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>9.286</v>
+        <v>1.184</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7157,313 +7078,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.59</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.554</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs Los Angeles Angels defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.807</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.467</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>5.131</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.807</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.633</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.244999999999999</v>
+        <v>5.131</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.061</v>
+        <v>7.776</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -7527,22 +7448,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.061</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.939</v>
+        <v>1.061</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7606,68 +7527,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.816000000000001</v>
+        <v>1.061</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.816000000000001</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5876</v>
+        <v>0.5946</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-142</v>
+        <v>-147</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6242</v>
+        <v>0.609</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-166</v>
+        <v>-156</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>122</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5336000000000001</v>
+        <v>0.5663</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>-131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9817,22 +9817,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4261</v>
+        <v>0.5336000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>135</v>
+        <v>-114</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,32 +9873,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Las Vegas Aces</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4261</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-108</v>
+        <v>135</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Indiana Fever @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10005,32 +10005,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5249</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5095</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-139</v>
+        <v>-104</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-122</v>
+        <v>107</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10213,22 +10213,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4124</v>
+        <v>0.5767</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>142</v>
+        <v>-136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>156</v>
+        <v>-122</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4012</v>
+        <v>0.3978</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>163</v>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Sky @ Dallas Wings</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.5125</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,26 +10401,26 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5125</v>
+        <v>0.512</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>-105</v>
@@ -13795,10 +13795,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4184</v>
+        <v>0.4233</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>122</v>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13861,10 +13861,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5816</v>
+        <v>0.5767</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-122</v>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.4337</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>113</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5663</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-115</v>
+        <v>-131</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>100</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4012</v>
+        <v>0.3978</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>163</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5988</v>
+        <v>0.6022000000000001</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-163</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.6242</v>
+        <v>0.609</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-166</v>
+        <v>-156</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>122</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3758</v>
+        <v>0.391</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>122</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4124</v>
+        <v>0.4054</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>156</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5876</v>
+        <v>0.5946</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-142</v>
+        <v>-147</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>178</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4608</v>
+        <v>0.4645</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5392</v>
+        <v>0.5355</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4079</v>
+        <v>0.4157</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 41.6% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5921</v>
+        <v>0.5843</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-145</v>
+        <v>-141</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4581</v>
+        <v>0.4548</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5419</v>
+        <v>0.5452</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4422</v>
+        <v>0.4429</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>126</v>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5578</v>
+        <v>0.5571</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>-126</v>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5392</v>
+        <v>0.538</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4608</v>
+        <v>0.462</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15374,7 +15374,7 @@
         <v>356</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15440,7 +15440,7 @@
         <v>-356</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15628,17 +15628,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings -9.5</t>
+          <t>Dallas Wings -11.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5162</v>
+        <v>0.4573601332209344</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-107</v>
+        <v>119</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-104</v>
+        <v>115</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -15694,17 +15694,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +9.5</t>
+          <t>Chicago Sky +11.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4838</v>
+        <v>0.5426398667790656</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>107</v>
+        <v>-119</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>-108</v>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15962,13 +15962,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4814000000000001</v>
+        <v>0.4802999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>108</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16024,17 +16024,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -6</t>
+          <t>Las Vegas Aces -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4520544547810846</v>
+        <v>0.4365025644033865</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16090,14 +16090,14 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever +6</t>
+          <t>Indiana Fever +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5167455452189154</v>
+        <v>0.5634974355966135</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-107</v>
+        <v>-129</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>138</v>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16166,7 +16166,7 @@
         <v>202</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>-105</v>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4762999999999999</v>
+        <v>0.4733000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16430,7 +16430,7 @@
         <v>138</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16562,7 +16562,7 @@
         <v>1157</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>733</v>
+        <v>669</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -17031,22 +17031,22 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>0.2488</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3956</v>
+        <v>0.3904</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-79.88</v>
+        <v>-87.88</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-13.45</v>
+        <v>-14.6</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>4.11</v>
@@ -17062,22 +17062,22 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>0.2497</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3921</v>
+        <v>0.3863</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-77.90000000000001</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-14.62</v>
+        <v>-15.88</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>5.86</v>
@@ -17166,7 +17166,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=414, ECE 0.045 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=416, ECE 0.042 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -17261,16 +17261,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.459</v>
+        <v>0.4591</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4297</v>
+        <v>0.4341</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0294</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="21">
@@ -17280,16 +17280,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5431</v>
+        <v>0.5432</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0047</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-12.xlsx
+++ b/data/output/workbook/2026-07-12.xlsx
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 19:04</t>
+          <t>2026-07-12 20:07</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,167 +3979,246 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Seattle Mariners offense vs Tampa Bay Rays defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.366</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>3.853</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>7.854</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>3.6</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.366</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.854</v>
+        <v>1.312</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -4203,22 +4282,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.312</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -4282,317 +4361,317 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.646000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.427</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.778</v>
+        <v>0.463</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Seattle Mariners defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.659</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.042</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.659</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.167</v>
+        <v>8.778</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.042</v>
+        <v>7.979</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -4656,22 +4735,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.979</v>
+        <v>0.958</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -4735,147 +4814,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.958</v>
+        <v>8.333</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.244</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.512</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.3</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.333</v>
+        <v>0.378</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,325 +5843,167 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.919</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.271</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.919</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>3.8</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.082</v>
+        <v>4.271</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6225,392 +6067,392 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>7.694</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.494</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.647</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.647</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>4.133</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.143</v>
+        <v>4.07</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.816</v>
+        <v>8.286</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6674,68 +6516,226 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.578</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.361</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6557999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-195</v>
+        <v>-191</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5946</v>
+        <v>0.5911</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8964,17 +8964,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.601</v>
+        <v>0.5674</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-151</v>
+        <v>-131</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.5974999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-130</v>
+        <v>-148</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5739000000000001</v>
+        <v>0.5796</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>170</v>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-156</v>
+        <v>-165</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>122</v>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5655</v>
+        <v>0.5637</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5575</v>
+        <v>0.5641</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-126</v>
+        <v>-129</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5501</v>
+        <v>0.5706</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>122</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9487,22 +9487,22 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5725</v>
+        <v>0.4326</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9553,22 +9553,22 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.434</v>
+        <v>0.5698</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>130</v>
+        <v>-132</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.399</v>
+        <v>0.4025</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>185</v>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.2% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Minnesota Twins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.5405</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-131</v>
+        <v>-118</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9817,22 +9817,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5336000000000001</v>
+        <v>0.4204</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-114</v>
+        <v>138</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9873,32 +9873,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4261</v>
+        <v>0.5362</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>135</v>
+        <v>-116</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9954,17 +9954,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 181</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10000,37 +10000,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Los Angeles Sparks @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Sparks +7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.5114000000000001</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10081,22 +10081,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4628</v>
+        <v>0.5249</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>116</v>
+        <v>-110</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -10147,22 +10147,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.4628</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-104</v>
+        <v>116</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5767</v>
+        <v>0.581</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>-139</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-122</v>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3978</v>
+        <v>0.4006</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>163</v>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Dallas Wings</t>
+          <t>Los Angeles Angels @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 178.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5125</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-105</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10401,32 +10401,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.512</v>
+        <v>0.4089</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-105</v>
+        <v>145</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4351</v>
+        <v>0.4306</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>118</v>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5649</v>
+        <v>0.5694</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-120</v>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5725</v>
+        <v>0.5698</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>111</v>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4275</v>
+        <v>0.4302</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-102</v>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.434</v>
+        <v>0.4326</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.5674</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4425</v>
+        <v>0.4363</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>100</v>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5575</v>
+        <v>0.5637</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-126</v>
+        <v>-129</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>129</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.422</v>
+        <v>0.4217</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>137</v>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5780000000000001</v>
+        <v>0.5783</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-137</v>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4471000000000001</v>
+        <v>0.4505</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>115</v>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11485,10 +11485,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5495</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-113</v>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11551,10 +11551,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4664</v>
+        <v>0.4595</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +114). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5336000000000001</v>
+        <v>0.5405</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-114</v>
+        <v>-118</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>112</v>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4261</v>
+        <v>0.4204</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>165</v>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5739000000000001</v>
+        <v>0.5796</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-135</v>
+        <v>-138</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>170</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.488</v>
+        <v>0.4877</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>105</v>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.512</v>
+        <v>0.5123</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-105</v>
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4499</v>
+        <v>0.4294</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>122</v>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5501</v>
+        <v>0.5706</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>122</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.6212</v>
+        <v>0.6226</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-156</v>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.3774</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>156</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -13135,10 +13135,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5655</v>
+        <v>0.5641</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>127</v>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13201,10 +13201,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4345</v>
+        <v>0.4359</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>105</v>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13267,10 +13267,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3392</v>
+        <v>0.3442</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>186</v>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 33.9% (fair +195). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6557999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-195</v>
+        <v>-191</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>186</v>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.5362</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-104</v>
+        <v>-116</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>107</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3983</v>
+        <v>0.3723</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>104</v>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.399</v>
+        <v>0.4025</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>185</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.2% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,10 +13729,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.601</v>
+        <v>0.5974999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-151</v>
+        <v>-148</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>163</v>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13795,10 +13795,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4233</v>
+        <v>0.419</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>122</v>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13861,10 +13861,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5767</v>
+        <v>0.581</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-136</v>
+        <v>-139</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-122</v>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.4733</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>113</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-131</v>
+        <v>-111</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>100</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3978</v>
+        <v>0.4006</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>163</v>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6022000000000001</v>
+        <v>0.5993999999999999</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-151</v>
+        <v>-150</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-163</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14323,10 +14323,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-156</v>
+        <v>-165</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>122</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14389,10 +14389,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.391</v>
+        <v>0.378</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>122</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4054</v>
+        <v>0.4089</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>156</v>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5946</v>
+        <v>0.5911</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>178</v>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.4638</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14651,10 +14651,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4548</v>
+        <v>0.4579</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5452</v>
+        <v>0.5421</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4429</v>
+        <v>0.4479</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5571</v>
+        <v>0.5521</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-126</v>
+        <v>-123</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.538</v>
+        <v>0.5542</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-116</v>
+        <v>-124</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.462</v>
+        <v>0.4458</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15440,7 +15440,7 @@
         <v>-356</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15704,7 +15704,7 @@
         <v>-119</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -15770,7 +15770,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15892,17 +15892,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 181</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -15958,17 +15958,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 181.5</t>
+          <t>Under 181</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4802999999999999</v>
+        <v>0.4551999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 180.5</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.5549727689112931</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-111</v>
+        <v>-125</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16354,17 +16354,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 180.5</t>
+          <t>Under 179.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4733000000000001</v>
+        <v>0.4450272310887069</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16420,17 +16420,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -8.5</t>
+          <t>Atlanta Dream -7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4210482224080958</v>
+        <v>0.4886</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16486,14 +16486,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +8.5</t>
+          <t>Los Angeles Sparks +7.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5789517775919042</v>
+        <v>0.5114000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-138</v>
+        <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>113</v>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -16820,10 +16820,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.486</v>
+        <v>0.4885</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-106</v>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -16886,13 +16886,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.514</v>
+        <v>0.5115000000000001</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -17031,22 +17031,22 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2488</v>
+        <v>0.249</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3904</v>
+        <v>0.3888</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-87.88</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-14.6</v>
+        <v>-15.03</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>4.11</v>
@@ -17062,22 +17062,22 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2497</v>
+        <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3863</v>
+        <v>0.3846</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-85.90000000000001</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-15.88</v>
+        <v>-16.35</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>5.86</v>
@@ -17166,7 +17166,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=416, ECE 0.042 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=417, ECE 0.043 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -17280,16 +17280,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.5432</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0022</v>
+        <v>-0.0052</v>
       </c>
     </row>
     <row r="22">
